--- a/assets/docs/movimiento.xlsx
+++ b/assets/docs/movimiento.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24729"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\cnomina\assets\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6C8864-1059-4214-A47D-E5D54A2A5ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5737F0BB-ACA2-4AD9-B56F-133B5C374091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MOVIMIENTO" sheetId="1" r:id="rId1"/>
@@ -487,19 +487,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -507,6 +494,15 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -516,7 +512,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -559,18 +555,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -607,53 +591,71 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -986,37 +988,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.2" x14ac:dyDescent="0.4">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="49"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="44"/>
     </row>
     <row r="2" spans="1:7" ht="16.2" x14ac:dyDescent="0.4">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="52"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="47"/>
     </row>
     <row r="3" spans="1:7" ht="16.2" x14ac:dyDescent="0.4">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="52"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="7"/>
@@ -1030,52 +1032,52 @@
       <c r="G4" s="9"/>
     </row>
     <row r="5" spans="1:7" ht="16.2" x14ac:dyDescent="0.4">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="36"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="32"/>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="54" t="s">
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="36"/>
+      <c r="G6" s="32"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="43"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="38"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="42"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="44"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="39"/>
       <c r="F8" s="22" t="s">
         <v>42</v>
       </c>
@@ -1170,34 +1172,34 @@
       <c r="G16" s="9"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="40" t="s">
+      <c r="A17" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="41"/>
-      <c r="C17" s="41" t="s">
+      <c r="B17" s="36"/>
+      <c r="C17" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41" t="s">
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="45"/>
+      <c r="G17" s="40"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="37" t="s">
+      <c r="A18" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="38"/>
-      <c r="C18" s="38" t="s">
+      <c r="B18" s="34"/>
+      <c r="C18" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38" t="s">
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="G18" s="39"/>
+      <c r="G18" s="35"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="7"/>
@@ -1218,22 +1220,22 @@
       <c r="G20" s="9"/>
     </row>
     <row r="21" spans="1:7" ht="16.2" x14ac:dyDescent="0.4">
-      <c r="A21" s="34" t="s">
+      <c r="A21" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="36"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="32"/>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="46"/>
-      <c r="C22" s="44"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="39"/>
       <c r="D22" s="3" t="s">
         <v>32</v>
       </c>
@@ -1248,9 +1250,9 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="53"/>
-      <c r="B23" s="46"/>
-      <c r="C23" s="44"/>
+      <c r="A23" s="48"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="39"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="3" t="s">
@@ -1271,10 +1273,10 @@
       <c r="D24" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="42" t="s">
+      <c r="E24" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="F24" s="44"/>
+      <c r="F24" s="39"/>
       <c r="G24" s="12" t="s">
         <v>17</v>
       </c>
@@ -1284,8 +1286,8 @@
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="44"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="39"/>
       <c r="G25" s="12"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1307,126 +1309,126 @@
       <c r="G27" s="9"/>
     </row>
     <row r="28" spans="1:7" ht="16.2" x14ac:dyDescent="0.4">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B28" s="35"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="36"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="32"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B29" s="42" t="s">
+      <c r="B29" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="C29" s="44"/>
-      <c r="D29" s="42" t="s">
+      <c r="C29" s="39"/>
+      <c r="D29" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="E29" s="44"/>
-      <c r="F29" s="42" t="s">
+      <c r="E29" s="39"/>
+      <c r="F29" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="G29" s="43"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G29" s="38"/>
+    </row>
+    <row r="30" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B30" s="32" t="s">
+      <c r="B30" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="33"/>
-      <c r="D30" s="32" t="s">
+      <c r="C30" s="29"/>
+      <c r="D30" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E30" s="33"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="25"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E30" s="29"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="53"/>
+    </row>
+    <row r="31" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="C31" s="29"/>
-      <c r="D31" s="28" t="s">
+      <c r="C31" s="25"/>
+      <c r="D31" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="E31" s="29"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="25"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E31" s="25"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="55"/>
+    </row>
+    <row r="32" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C32" s="29"/>
-      <c r="D32" s="28" t="s">
+      <c r="C32" s="25"/>
+      <c r="D32" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E32" s="29"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="25"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E32" s="25"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="55"/>
+    </row>
+    <row r="33" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="16"/>
-      <c r="B33" s="28" t="s">
+      <c r="B33" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="29"/>
-      <c r="D33" s="28" t="s">
+      <c r="C33" s="25"/>
+      <c r="D33" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="E33" s="29"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="25"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E33" s="25"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="55"/>
+    </row>
+    <row r="34" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="16"/>
-      <c r="B34" s="28" t="s">
+      <c r="B34" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="29"/>
+      <c r="C34" s="25"/>
       <c r="D34" s="5"/>
       <c r="E34" s="6"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="25"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F34" s="54"/>
+      <c r="G34" s="55"/>
+    </row>
+    <row r="35" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="16"/>
-      <c r="B35" s="28" t="s">
+      <c r="B35" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="29"/>
+      <c r="C35" s="25"/>
       <c r="D35" s="5"/>
       <c r="E35" s="6"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="25"/>
-    </row>
-    <row r="36" spans="1:7" ht="12.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F35" s="54"/>
+      <c r="G35" s="55"/>
+    </row>
+    <row r="36" spans="1:7" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="17"/>
-      <c r="B36" s="30" t="s">
+      <c r="B36" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="31"/>
+      <c r="C36" s="27"/>
       <c r="D36" s="18"/>
       <c r="E36" s="19"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="27"/>
+      <c r="F36" s="56"/>
+      <c r="G36" s="57"/>
     </row>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="36">
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
@@ -1448,13 +1450,12 @@
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F17:G17"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="A28:G28"/>
+    <mergeCell ref="F30:G36"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B35:C35"/>
@@ -1462,13 +1463,8 @@
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/assets/docs/movimiento.xlsx
+++ b/assets/docs/movimiento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\cnomina\assets\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5737F0BB-ACA2-4AD9-B56F-133B5C374091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CBC24A-087A-406E-A386-476C9FFCB756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
   <si>
     <t>DEPARTAMENTO DE RECURSOS HUMANOS</t>
   </si>
@@ -181,9 +181,6 @@
   </si>
   <si>
     <t>(  ) MATERNAL</t>
-  </si>
-  <si>
-    <t>BASE (  )  CONFIANZA (  ) EVENTUAL (  )</t>
   </si>
   <si>
     <t>(  ) PRORROGA DE LICENCIA</t>
@@ -512,7 +509,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -555,12 +552,96 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -573,89 +654,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -988,37 +988,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.2" x14ac:dyDescent="0.4">
-      <c r="A1" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="44"/>
+      <c r="A1" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="31"/>
     </row>
     <row r="2" spans="1:7" ht="16.2" x14ac:dyDescent="0.4">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="47"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="34"/>
     </row>
     <row r="3" spans="1:7" ht="16.2" x14ac:dyDescent="0.4">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="34"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="7"/>
@@ -1027,57 +1027,55 @@
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G4" s="9"/>
     </row>
     <row r="5" spans="1:7" ht="16.2" x14ac:dyDescent="0.4">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="32"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="39"/>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="49" t="s">
+      <c r="B6" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="49" t="s">
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="32"/>
+      <c r="G6" s="39"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="37" t="s">
+      <c r="A7" s="58"/>
+      <c r="B7" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="38"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="41"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="39"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="26"/>
       <c r="F8" s="22" t="s">
         <v>42</v>
       </c>
@@ -1172,34 +1170,34 @@
       <c r="G16" s="9"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="51" t="s">
+      <c r="A17" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="36"/>
-      <c r="C17" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17" s="40"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" s="44"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="33" t="s">
+      <c r="A18" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="34"/>
-      <c r="C18" s="34" t="s">
+      <c r="B18" s="46"/>
+      <c r="C18" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18" s="35"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18" s="47"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="7"/>
@@ -1220,22 +1218,22 @@
       <c r="G20" s="9"/>
     </row>
     <row r="21" spans="1:7" ht="16.2" x14ac:dyDescent="0.4">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="32"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="39"/>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="41"/>
-      <c r="C22" s="39"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="26"/>
       <c r="D22" s="3" t="s">
         <v>32</v>
       </c>
@@ -1250,9 +1248,9 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="48"/>
-      <c r="B23" s="41"/>
-      <c r="C23" s="39"/>
+      <c r="A23" s="35"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="26"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="3" t="s">
@@ -1273,10 +1271,10 @@
       <c r="D24" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="37" t="s">
+      <c r="E24" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="F24" s="39"/>
+      <c r="F24" s="26"/>
       <c r="G24" s="12" t="s">
         <v>17</v>
       </c>
@@ -1286,8 +1284,8 @@
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="39"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="26"/>
       <c r="G25" s="12"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1309,126 +1307,146 @@
       <c r="G27" s="9"/>
     </row>
     <row r="28" spans="1:7" ht="16.2" x14ac:dyDescent="0.4">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="32"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="39"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B29" s="37" t="s">
+      <c r="B29" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="C29" s="39"/>
-      <c r="D29" s="37" t="s">
+      <c r="C29" s="26"/>
+      <c r="D29" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="E29" s="39"/>
-      <c r="F29" s="37" t="s">
+      <c r="E29" s="26"/>
+      <c r="F29" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="G29" s="38"/>
+      <c r="G29" s="41"/>
     </row>
     <row r="30" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B30" s="28" t="s">
+      <c r="B30" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="29"/>
-      <c r="D30" s="28" t="s">
+      <c r="C30" s="57"/>
+      <c r="D30" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="E30" s="29"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="53"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="49"/>
     </row>
     <row r="31" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="24" t="s">
+      <c r="B31" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C31" s="25"/>
-      <c r="D31" s="24" t="s">
+      <c r="C31" s="28"/>
+      <c r="D31" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="E31" s="25"/>
-      <c r="F31" s="54"/>
-      <c r="G31" s="55"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="51"/>
     </row>
     <row r="32" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C32" s="25"/>
-      <c r="D32" s="24" t="s">
+      <c r="C32" s="28"/>
+      <c r="D32" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="E32" s="25"/>
-      <c r="F32" s="54"/>
-      <c r="G32" s="55"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="51"/>
     </row>
     <row r="33" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="16"/>
-      <c r="B33" s="24" t="s">
+      <c r="B33" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="25"/>
-      <c r="D33" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="E33" s="25"/>
-      <c r="F33" s="54"/>
-      <c r="G33" s="55"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="28"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="51"/>
     </row>
     <row r="34" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="16"/>
-      <c r="B34" s="24" t="s">
+      <c r="B34" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="25"/>
+      <c r="C34" s="28"/>
       <c r="D34" s="5"/>
       <c r="E34" s="6"/>
-      <c r="F34" s="54"/>
-      <c r="G34" s="55"/>
+      <c r="F34" s="50"/>
+      <c r="G34" s="51"/>
     </row>
     <row r="35" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="16"/>
-      <c r="B35" s="24" t="s">
+      <c r="B35" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="25"/>
+      <c r="C35" s="28"/>
       <c r="D35" s="5"/>
       <c r="E35" s="6"/>
-      <c r="F35" s="54"/>
-      <c r="G35" s="55"/>
+      <c r="F35" s="50"/>
+      <c r="G35" s="51"/>
     </row>
     <row r="36" spans="1:7" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="17"/>
-      <c r="B36" s="26" t="s">
+      <c r="B36" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="27"/>
+      <c r="C36" s="55"/>
       <c r="D36" s="18"/>
       <c r="E36" s="19"/>
-      <c r="F36" s="56"/>
-      <c r="G36" s="57"/>
+      <c r="F36" s="52"/>
+      <c r="G36" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="F30:G36"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="A28:G28"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
@@ -1445,26 +1463,6 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="F30:G36"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/assets/docs/movimiento.xlsx
+++ b/assets/docs/movimiento.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\cnomina\assets\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nick\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ECADD9C-15F9-4B74-BCB4-36F70E154137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24631743-1375-4E0A-8199-1319546CB4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="252" windowWidth="23256" windowHeight="11952" xr2:uid="{6D904949-6251-49AB-B7B7-4090CE89A75B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{6D904949-6251-49AB-B7B7-4090CE89A75B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,6 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -147,8 +146,11 @@
     <t>DEPARTAMENTO DESTINO</t>
   </si>
   <si>
+    <t>NO. DE PERIODO CATORCENAL</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">PRESIDENCIA MUNICIPAL DE COMONFORT
+      <t xml:space="preserve">PRESIDENCIA MUNICIPAL DE SANTIAGO MARAVATIO
 </t>
     </r>
     <r>
@@ -161,9 +163,6 @@
       </rPr>
       <t>ADMINISTRACIÓN 2021-2024</t>
     </r>
-  </si>
-  <si>
-    <t>NO. DE PERIODO CATORCENAL</t>
   </si>
 </sst>
 </file>
@@ -443,6 +442,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -452,6 +460,60 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -468,69 +530,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -896,25 +895,25 @@
     </row>
     <row r="3" spans="2:20" ht="49.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="5"/>
-      <c r="C3" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="41"/>
-      <c r="R3" s="41"/>
-      <c r="S3" s="42"/>
+      <c r="C3" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="31"/>
+      <c r="P3" s="31"/>
+      <c r="Q3" s="31"/>
+      <c r="R3" s="31"/>
+      <c r="S3" s="32"/>
       <c r="T3" s="6"/>
     </row>
     <row r="4" spans="2:20" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -945,21 +944,21 @@
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="47"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="37"/>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
       <c r="N5" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O5" s="7"/>
       <c r="Q5" s="7"/>
-      <c r="R5" s="27"/>
-      <c r="S5" s="29"/>
+      <c r="R5" s="18"/>
+      <c r="S5" s="20"/>
       <c r="T5" s="6"/>
     </row>
     <row r="6" spans="2:20" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -985,25 +984,25 @@
     </row>
     <row r="7" spans="2:20" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="5"/>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="38"/>
-      <c r="N7" s="38"/>
-      <c r="O7" s="38"/>
-      <c r="P7" s="38"/>
-      <c r="Q7" s="38"/>
-      <c r="R7" s="38"/>
-      <c r="S7" s="39"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="28"/>
+      <c r="R7" s="28"/>
+      <c r="S7" s="29"/>
       <c r="T7" s="6"/>
     </row>
     <row r="8" spans="2:20" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1029,29 +1028,29 @@
     </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B9" s="5"/>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="20"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="23"/>
       <c r="G9" s="7"/>
-      <c r="H9" s="18" t="s">
+      <c r="H9" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="20"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="23"/>
       <c r="N9" s="7"/>
-      <c r="O9" s="18" t="s">
+      <c r="O9" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="19"/>
-      <c r="S9" s="20"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="22"/>
+      <c r="S9" s="23"/>
       <c r="T9" s="6"/>
     </row>
     <row r="10" spans="2:20" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1215,25 +1214,25 @@
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B17" s="5"/>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="19"/>
-      <c r="S17" s="20"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="22"/>
+      <c r="S17" s="23"/>
       <c r="T17" s="6"/>
     </row>
     <row r="18" spans="2:20" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1263,22 +1262,22 @@
       <c r="D19" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="E19" s="27"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="29"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="20"/>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
-      <c r="L19" s="30" t="s">
+      <c r="L19" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="M19" s="30"/>
-      <c r="N19" s="30"/>
-      <c r="O19" s="27"/>
-      <c r="P19" s="28"/>
-      <c r="Q19" s="28"/>
-      <c r="R19" s="29"/>
+      <c r="M19" s="38"/>
+      <c r="N19" s="38"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="20"/>
       <c r="S19" s="6"/>
       <c r="T19" s="6"/>
     </row>
@@ -1330,11 +1329,11 @@
       <c r="D22" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="34"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="36"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="26"/>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
       <c r="L22" s="7" t="s">
@@ -1342,10 +1341,10 @@
       </c>
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
-      <c r="O22" s="27"/>
-      <c r="P22" s="28"/>
-      <c r="Q22" s="28"/>
-      <c r="R22" s="29"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
+      <c r="R22" s="20"/>
       <c r="S22" s="6"/>
       <c r="T22" s="6"/>
     </row>
@@ -1393,25 +1392,25 @@
     </row>
     <row r="25" spans="2:20" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="5"/>
-      <c r="C25" s="37" t="s">
+      <c r="C25" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="43"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="43"/>
-      <c r="I25" s="43"/>
-      <c r="J25" s="43"/>
-      <c r="K25" s="43"/>
-      <c r="L25" s="43"/>
-      <c r="M25" s="43"/>
-      <c r="N25" s="43"/>
-      <c r="O25" s="43"/>
-      <c r="P25" s="43"/>
-      <c r="Q25" s="43"/>
-      <c r="R25" s="43"/>
-      <c r="S25" s="44"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="33"/>
+      <c r="N25" s="33"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="33"/>
+      <c r="Q25" s="33"/>
+      <c r="R25" s="33"/>
+      <c r="S25" s="34"/>
       <c r="T25" s="6"/>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.3">
@@ -1463,10 +1462,10 @@
       </c>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="29"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="20"/>
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="7" t="s">
@@ -1475,10 +1474,10 @@
       <c r="M28" s="7"/>
       <c r="N28" s="7"/>
       <c r="O28" s="7"/>
-      <c r="P28" s="27"/>
-      <c r="Q28" s="28"/>
-      <c r="R28" s="28"/>
-      <c r="S28" s="29"/>
+      <c r="P28" s="18"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="20"/>
       <c r="T28" s="6"/>
     </row>
     <row r="29" spans="2:20" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1509,10 +1508,10 @@
       </c>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="29"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="20"/>
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
       <c r="L30" s="7" t="s">
@@ -1521,10 +1520,10 @@
       <c r="M30" s="7"/>
       <c r="N30" s="7"/>
       <c r="O30" s="7"/>
-      <c r="P30" s="27"/>
-      <c r="Q30" s="28"/>
-      <c r="R30" s="28"/>
-      <c r="S30" s="29"/>
+      <c r="P30" s="18"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="20"/>
       <c r="T30" s="6"/>
     </row>
     <row r="31" spans="2:20" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1555,10 +1554,10 @@
       </c>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="29"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="20"/>
       <c r="J32" s="7"/>
       <c r="K32" s="7"/>
       <c r="L32" s="7" t="s">
@@ -1567,10 +1566,10 @@
       <c r="M32" s="7"/>
       <c r="N32" s="7"/>
       <c r="O32" s="7"/>
-      <c r="P32" s="27"/>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="28"/>
-      <c r="S32" s="29"/>
+      <c r="P32" s="18"/>
+      <c r="Q32" s="19"/>
+      <c r="R32" s="19"/>
+      <c r="S32" s="20"/>
       <c r="T32" s="6"/>
     </row>
     <row r="33" spans="2:20" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1596,25 +1595,25 @@
     </row>
     <row r="34" spans="2:20" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B34" s="5"/>
-      <c r="C34" s="31" t="s">
+      <c r="C34" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="D34" s="32"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="32"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="32"/>
-      <c r="L34" s="32"/>
-      <c r="M34" s="32"/>
-      <c r="N34" s="32"/>
-      <c r="O34" s="32"/>
-      <c r="P34" s="32"/>
-      <c r="Q34" s="32"/>
-      <c r="R34" s="32"/>
-      <c r="S34" s="33"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="40"/>
+      <c r="I34" s="40"/>
+      <c r="J34" s="40"/>
+      <c r="K34" s="40"/>
+      <c r="L34" s="40"/>
+      <c r="M34" s="40"/>
+      <c r="N34" s="40"/>
+      <c r="O34" s="40"/>
+      <c r="P34" s="40"/>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="40"/>
+      <c r="S34" s="41"/>
       <c r="T34" s="6"/>
     </row>
     <row r="35" spans="2:20" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1647,18 +1646,18 @@
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="28"/>
-      <c r="K36" s="28"/>
-      <c r="L36" s="28"/>
-      <c r="M36" s="28"/>
-      <c r="N36" s="28"/>
-      <c r="O36" s="28"/>
-      <c r="P36" s="28"/>
-      <c r="Q36" s="28"/>
-      <c r="R36" s="28"/>
-      <c r="S36" s="29"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="19"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="19"/>
+      <c r="M36" s="19"/>
+      <c r="N36" s="19"/>
+      <c r="O36" s="19"/>
+      <c r="P36" s="19"/>
+      <c r="Q36" s="19"/>
+      <c r="R36" s="19"/>
+      <c r="S36" s="20"/>
       <c r="T36" s="6"/>
     </row>
     <row r="37" spans="2:20" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1688,12 +1687,12 @@
         <v>21</v>
       </c>
       <c r="D38" s="7"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="29"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="20"/>
       <c r="K38" s="17"/>
       <c r="L38" s="7"/>
       <c r="M38" s="7" t="s">
@@ -1702,9 +1701,9 @@
       <c r="N38" s="7"/>
       <c r="O38" s="7"/>
       <c r="P38" s="7"/>
-      <c r="Q38" s="27"/>
-      <c r="R38" s="28"/>
-      <c r="S38" s="29"/>
+      <c r="Q38" s="18"/>
+      <c r="R38" s="19"/>
+      <c r="S38" s="20"/>
       <c r="T38" s="6"/>
     </row>
     <row r="39" spans="2:20" x14ac:dyDescent="0.3">
@@ -1751,25 +1750,25 @@
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B41" s="5"/>
-      <c r="C41" s="18" t="s">
+      <c r="C41" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
-      <c r="N41" s="19"/>
-      <c r="O41" s="19"/>
-      <c r="P41" s="19"/>
-      <c r="Q41" s="19"/>
-      <c r="R41" s="19"/>
-      <c r="S41" s="20"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22"/>
+      <c r="N41" s="22"/>
+      <c r="O41" s="22"/>
+      <c r="P41" s="22"/>
+      <c r="Q41" s="22"/>
+      <c r="R41" s="22"/>
+      <c r="S41" s="23"/>
       <c r="T41" s="6"/>
     </row>
     <row r="42" spans="2:20" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1885,27 +1884,27 @@
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B47" s="5"/>
-      <c r="C47" s="18" t="s">
+      <c r="C47" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="19"/>
-      <c r="I47" s="19"/>
-      <c r="J47" s="19"/>
-      <c r="K47" s="20"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="22"/>
+      <c r="H47" s="22"/>
+      <c r="I47" s="22"/>
+      <c r="J47" s="22"/>
+      <c r="K47" s="23"/>
       <c r="L47" s="9"/>
-      <c r="M47" s="18" t="s">
+      <c r="M47" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="N47" s="19"/>
-      <c r="O47" s="19"/>
-      <c r="P47" s="19"/>
-      <c r="Q47" s="19"/>
-      <c r="R47" s="19"/>
-      <c r="S47" s="20"/>
+      <c r="N47" s="22"/>
+      <c r="O47" s="22"/>
+      <c r="P47" s="22"/>
+      <c r="Q47" s="22"/>
+      <c r="R47" s="22"/>
+      <c r="S47" s="23"/>
       <c r="T47" s="6"/>
     </row>
     <row r="48" spans="2:20" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1935,20 +1934,20 @@
       <c r="D49" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E49" s="27"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="28"/>
-      <c r="J49" s="29"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="19"/>
+      <c r="I49" s="19"/>
+      <c r="J49" s="20"/>
       <c r="K49" s="6"/>
       <c r="L49" s="7"/>
       <c r="M49" s="5"/>
-      <c r="N49" s="21"/>
-      <c r="O49" s="22"/>
-      <c r="P49" s="22"/>
-      <c r="Q49" s="22"/>
-      <c r="R49" s="23"/>
+      <c r="N49" s="42"/>
+      <c r="O49" s="43"/>
+      <c r="P49" s="43"/>
+      <c r="Q49" s="43"/>
+      <c r="R49" s="44"/>
       <c r="S49" s="6"/>
       <c r="T49" s="6"/>
     </row>
@@ -1965,11 +1964,11 @@
       <c r="K50" s="6"/>
       <c r="L50" s="7"/>
       <c r="M50" s="5"/>
-      <c r="N50" s="24"/>
-      <c r="O50" s="25"/>
-      <c r="P50" s="25"/>
-      <c r="Q50" s="25"/>
-      <c r="R50" s="26"/>
+      <c r="N50" s="45"/>
+      <c r="O50" s="46"/>
+      <c r="P50" s="46"/>
+      <c r="Q50" s="46"/>
+      <c r="R50" s="47"/>
       <c r="S50" s="6"/>
       <c r="T50" s="6"/>
     </row>
@@ -1979,12 +1978,12 @@
       <c r="D51" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E51" s="27"/>
-      <c r="F51" s="28"/>
-      <c r="G51" s="28"/>
-      <c r="H51" s="28"/>
-      <c r="I51" s="28"/>
-      <c r="J51" s="29"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="19"/>
+      <c r="I51" s="19"/>
+      <c r="J51" s="20"/>
       <c r="K51" s="6"/>
       <c r="L51" s="7"/>
       <c r="M51" s="5"/>
@@ -2009,11 +2008,11 @@
       <c r="K52" s="6"/>
       <c r="L52" s="7"/>
       <c r="M52" s="5"/>
-      <c r="N52" s="21"/>
-      <c r="O52" s="22"/>
-      <c r="P52" s="22"/>
-      <c r="Q52" s="22"/>
-      <c r="R52" s="23"/>
+      <c r="N52" s="42"/>
+      <c r="O52" s="43"/>
+      <c r="P52" s="43"/>
+      <c r="Q52" s="43"/>
+      <c r="R52" s="44"/>
       <c r="S52" s="6"/>
       <c r="T52" s="6"/>
     </row>
@@ -2023,20 +2022,20 @@
       <c r="D53" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E53" s="21"/>
-      <c r="F53" s="22"/>
-      <c r="G53" s="22"/>
-      <c r="H53" s="22"/>
-      <c r="I53" s="22"/>
-      <c r="J53" s="23"/>
+      <c r="E53" s="42"/>
+      <c r="F53" s="43"/>
+      <c r="G53" s="43"/>
+      <c r="H53" s="43"/>
+      <c r="I53" s="43"/>
+      <c r="J53" s="44"/>
       <c r="K53" s="6"/>
       <c r="L53" s="7"/>
       <c r="M53" s="5"/>
-      <c r="N53" s="24"/>
-      <c r="O53" s="25"/>
-      <c r="P53" s="25"/>
-      <c r="Q53" s="25"/>
-      <c r="R53" s="26"/>
+      <c r="N53" s="45"/>
+      <c r="O53" s="46"/>
+      <c r="P53" s="46"/>
+      <c r="Q53" s="46"/>
+      <c r="R53" s="47"/>
       <c r="S53" s="6"/>
       <c r="T53" s="6"/>
     </row>
@@ -2044,12 +2043,12 @@
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
       <c r="D54" s="7"/>
-      <c r="E54" s="24"/>
-      <c r="F54" s="25"/>
-      <c r="G54" s="25"/>
-      <c r="H54" s="25"/>
-      <c r="I54" s="25"/>
-      <c r="J54" s="26"/>
+      <c r="E54" s="45"/>
+      <c r="F54" s="46"/>
+      <c r="G54" s="46"/>
+      <c r="H54" s="46"/>
+      <c r="I54" s="46"/>
+      <c r="J54" s="47"/>
       <c r="K54" s="6"/>
       <c r="L54" s="7"/>
       <c r="M54" s="5"/>
@@ -2074,11 +2073,11 @@
       <c r="K55" s="6"/>
       <c r="L55" s="7"/>
       <c r="M55" s="5"/>
-      <c r="N55" s="21"/>
-      <c r="O55" s="22"/>
-      <c r="P55" s="22"/>
-      <c r="Q55" s="22"/>
-      <c r="R55" s="23"/>
+      <c r="N55" s="42"/>
+      <c r="O55" s="43"/>
+      <c r="P55" s="43"/>
+      <c r="Q55" s="43"/>
+      <c r="R55" s="44"/>
       <c r="S55" s="6"/>
       <c r="T55" s="6"/>
     </row>
@@ -2088,20 +2087,20 @@
       <c r="D56" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E56" s="27"/>
-      <c r="F56" s="28"/>
-      <c r="G56" s="28"/>
-      <c r="H56" s="28"/>
-      <c r="I56" s="28"/>
-      <c r="J56" s="29"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="19"/>
+      <c r="G56" s="19"/>
+      <c r="H56" s="19"/>
+      <c r="I56" s="19"/>
+      <c r="J56" s="20"/>
       <c r="K56" s="6"/>
       <c r="L56" s="7"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="24"/>
-      <c r="O56" s="25"/>
-      <c r="P56" s="25"/>
-      <c r="Q56" s="25"/>
-      <c r="R56" s="26"/>
+      <c r="N56" s="45"/>
+      <c r="O56" s="46"/>
+      <c r="P56" s="46"/>
+      <c r="Q56" s="46"/>
+      <c r="R56" s="47"/>
       <c r="S56" s="6"/>
       <c r="T56" s="6"/>
     </row>
@@ -2149,33 +2148,6 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="H36:S36"/>
-    <mergeCell ref="O9:S9"/>
-    <mergeCell ref="F32:I32"/>
-    <mergeCell ref="O22:R22"/>
-    <mergeCell ref="E22:I22"/>
-    <mergeCell ref="C7:S7"/>
-    <mergeCell ref="C3:S3"/>
-    <mergeCell ref="C25:S25"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="C41:S41"/>
-    <mergeCell ref="C47:K47"/>
-    <mergeCell ref="P28:S28"/>
-    <mergeCell ref="P30:S30"/>
-    <mergeCell ref="P32:S32"/>
-    <mergeCell ref="C17:S17"/>
-    <mergeCell ref="E38:J38"/>
-    <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="E19:I19"/>
-    <mergeCell ref="C34:S34"/>
-    <mergeCell ref="F28:I28"/>
-    <mergeCell ref="F30:I30"/>
-    <mergeCell ref="M47:S47"/>
     <mergeCell ref="N49:R50"/>
     <mergeCell ref="N52:R53"/>
     <mergeCell ref="N55:R56"/>
@@ -2183,6 +2155,33 @@
     <mergeCell ref="E51:J51"/>
     <mergeCell ref="E53:J54"/>
     <mergeCell ref="E56:J56"/>
+    <mergeCell ref="C41:S41"/>
+    <mergeCell ref="C47:K47"/>
+    <mergeCell ref="P28:S28"/>
+    <mergeCell ref="P30:S30"/>
+    <mergeCell ref="P32:S32"/>
+    <mergeCell ref="E38:J38"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="C34:S34"/>
+    <mergeCell ref="F28:I28"/>
+    <mergeCell ref="F30:I30"/>
+    <mergeCell ref="M47:S47"/>
+    <mergeCell ref="C7:S7"/>
+    <mergeCell ref="C3:S3"/>
+    <mergeCell ref="C25:S25"/>
+    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="C17:S17"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="E19:I19"/>
+    <mergeCell ref="H36:S36"/>
+    <mergeCell ref="O9:S9"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="O22:R22"/>
+    <mergeCell ref="E22:I22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="72" orientation="portrait" r:id="rId1"/>
